--- a/Capstone_use_cases.xlsx
+++ b/Capstone_use_cases.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashwinanandram/Documents/GitHub/User Propensity Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7032E8-890A-B64A-8495-12F2EBF44E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71111E04-1D38-D74D-A42D-B5A127D74E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Domain-Capstoneusecase-TypicalM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -940,6 +952,240 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{22753382-E775-FD41-8D7A-6326F9D0657B}">
+  <we:reference id="wa200010884" version="1.0.0.2" store="en-GB" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200010884" version="1.0.0.2" store="wa200010884" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_STAT_ACF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ACOVF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ADFULLER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ALEXANDERGOVERN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ANDERSON_KSAMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ANOVA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ANSARI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ARIMA_FORECAST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ARMA_ORDER_IC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BARNARD_EXACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BARTLETT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BAYES_MVS_CI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BB_LOGBETA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BB_POST_UPDATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BB_QBETA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BERNOULLI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BETA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BETA_CI_BOUNDS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BETABINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BETANBINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BINNED_STATISTIC</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BINNED_STATISTIC_2D</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BINOMTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BOLTZMANN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BOSCHLOO_EXACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BRUNNERMUNZEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_BWS_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CANCORR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CAUCHY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CCF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CCOVF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CHI2_CONTINGENCY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CHISQ</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_COX_HAZARDS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CRONBACH_ALPHA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CUMFREQ</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_CVM_2SAMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DESCRIBE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DETREND</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DIRICHLET</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DIRICHLET_MULTINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DISTANCE_CORR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DLAPLACE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_CRED_INT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_DIRICHLET_SUM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_LOGBETA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_LOGSUM_NORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_POST_UPDATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DM_PREDICTIVE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_DUNNETT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EMA_LFILTER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EMA_PERIOD</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EPPS_SINGLE_2SAMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EXP_SURVIVAL_REG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EXPECTILE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_EXPON</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_F_DIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_F_ONEWAY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_FACTOR_ANALYSIS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_FISHER_EXACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_FLIGNER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_FRIEDMANCHISQUARE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GAMESHOWELL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GAMMA_CI_BOUNDS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GAMMA_POST_Q</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GEE_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GEOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_BINOMIAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_GAMMA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_INV_GAUSS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_NEG_BINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_POISSON</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLM_TWEEDIE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLMM_BINOMIAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLMM_POISSON</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GLS_REGRESSION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_GMEAN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HANNAN_RISSANEN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HMEAN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HOLT_FORECAST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HOMOSCEDASTICITY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HURDLE_COUNT_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HW_FORECAST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_HYPERGEOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_INFLUENCE_DIAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_INNOVATIONS_MLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_INVGAMMA_CI_BOUNDS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_INVGAMMA_POST_Q</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_JARQUE_BERA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KAPLAN_MEIER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KENDALLTAU</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KPSS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KRUSKAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KS_2SAMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KSTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KURTOSIS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_KURTOSISTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LAPLACE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LEVENE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LINREGRESS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LOGIT_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LOGNORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_LOGSER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MANNWHITNEYU</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MANOVA_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MATRIX_NORMAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MEDIAN_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MEDIATION_ANALYSIS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MIXED_ANOVA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MIXED_LINEAR_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MODE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MOMENT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MOOD</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MSTL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MULTINOMIAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MULTINOMIAL_LOGIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MULTISCALE_GRAPH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MULTIVARIATE_NORMAL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MULTIVARIATE_T</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MV_HYPERGEOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_MVSDIST_CI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NBINOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NHYPERGEOM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NIG_POST_UPDATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NN_POST_UPDATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NORMALITY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_NORMALTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_OLS_DIAGNOSTICS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_OLS_REGRESSION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ORDERED_LOGIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ORTHO_GROUP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PACF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PAGE_TREND_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PAIRWISE_TUKEY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PARETO</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PARTIAL_CORR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PCA_ANALYSIS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PEARSONR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PERCENTILEOFSCORE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PERIODOGRAM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PLANCK</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PMEAN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POINTBISERIALR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POISSON_DIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POISSON_MEANS_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_BMV</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_ENTROPY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_LOGSUMEXP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_MAP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_TAILPROB</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_WMEANVAR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_POSTERIOR_XLOGY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_PROBIT_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_Q_STAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_QUANTILE_REGRESSION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_QUANTILE_TEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RANDINT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RANDOM_CORRELATION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RANKSUMS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_REGRESS_DIAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RELFREQ</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RM_ANOVA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ROBUST_LINEAR_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_RURTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SAMPLE_EQTAIL_CI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SAMPLE_HPD_CI</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SARIMAX_FORECAST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SCOREATPERCENTILE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SEASDECOMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SES_FORECAST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SHAPIRO</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SIEGELSLOPES</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SKELLAM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SKEWNESS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SKEWTEST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SMA_CONV</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SMA_CUMSUM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SOMERSD</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SPEARMANR</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SPECIAL_ORTHO_GROUP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_SPECIFICATION_TESTS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_STL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_T_DIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_THEILSLOPES</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_TTEST_1SAMP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_TTEST_IND</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_TTEST_IND_STATS</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_UNIFORM</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_UNIFORM_DIRECTION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_UNITARY_GROUP</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_VAL_DISCRETE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_VONMISES_FISHER</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WEIBULL_MIN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WEIGHTEDTAU</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WELCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WELCH_ANOVA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WINMA_CONV</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WISHART</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WLS_REGRESSION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_WMA</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_YULESIMON</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ZINB_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ZIP_MODEL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ZIPF</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ZIPFIAN</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_STAT_ZIVOT_ANDREWS</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
